--- a/survey_templates/031_social_dynamics_assessment--survey_templates.xlsx
+++ b/survey_templates/031_social_dynamics_assessment--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -822,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1110,29 +1110,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compromising</t>
+          <t>conceding</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Compromising</t>
+          <t>Conceding</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>team_roles_choices</t>
+          <t>decision_making_process_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>conceding</t>
+          <t>autocratic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Conceding</t>
+          <t>Autocratic</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>autocratic</t>
+          <t>participative</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Autocratic</t>
+          <t>Participative</t>
         </is>
       </c>
     </row>
@@ -1161,29 +1161,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>participative</t>
+          <t>consensus</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Participative</t>
+          <t>Consensus</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>decision_making_process_choices</t>
+          <t>team_satisfaction_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>consensus</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Consensus</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1195,29 +1195,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>team_satisfaction_choices</t>
+          <t>team_satisfaction_reasons_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>good_team_spirit</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Good team spirit</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>good_team_spirit</t>
+          <t>clear_goals</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Good team spirit</t>
+          <t>Clear goals</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>clear_goals</t>
+          <t>effective_communication</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Clear goals</t>
+          <t>Effective communication</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>effective_communication</t>
+          <t>positive_attitude</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Effective communication</t>
+          <t>Positive attitude</t>
         </is>
       </c>
     </row>
@@ -1280,27 +1280,10 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>positive_attitude</t>
+          <t>good_team_work</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
-        <is>
-          <t>Positive attitude</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>team_satisfaction_reasons_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>good_team_work</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>Good team work</t>
         </is>
